--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC3">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G2">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00:00</t>
+          <t>2026-10-05 10:00:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G3">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-05 15:30:00</t>
+          <t>2026-10-05 11:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:05:00</t>
+          <t>2026-10-05 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,156 +1077,645 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Norway First Division</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N5">
+        <v>4.31</v>
+      </c>
+      <c r="O5">
+        <v>4.5</v>
+      </c>
+      <c r="P5">
+        <v>1.6</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-1</v>
+      </c>
+      <c r="AN5">
+        <v>-1</v>
+      </c>
+      <c r="AO5">
+        <v>-1</v>
+      </c>
+      <c r="AP5">
+        <v>-1</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CD Tenerife</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N6">
+        <v>1.96</v>
+      </c>
+      <c r="O6">
+        <v>3.63</v>
+      </c>
+      <c r="P6">
+        <v>3.9</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>1.82</v>
+      </c>
+      <c r="AB6">
+        <v>1.87</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-1</v>
+      </c>
+      <c r="AN6">
+        <v>-1</v>
+      </c>
+      <c r="AO6">
+        <v>-1</v>
+      </c>
+      <c r="AP6">
+        <v>-1</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chapelton</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Portmore United</t>
         </is>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-1</v>
-      </c>
-      <c r="AN5">
-        <v>-1</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>-1</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>2026-10-05 22:00:00</t>
         </is>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-05 19:05:00</t>
+          <t>2026-10-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,156 +1566,319 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Chapelton</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Portmore United</t>
         </is>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-1</v>
-      </c>
-      <c r="AN8">
-        <v>-1</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>-1</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-1</v>
+      </c>
+      <c r="AN9">
+        <v>-1</v>
+      </c>
+      <c r="AO9">
+        <v>-1</v>
+      </c>
+      <c r="AP9">
+        <v>-1</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>2026-10-05 22:00:00</t>
         </is>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1296,34 +1296,34 @@
         <v>3.9</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
         <v>1.82</v>
@@ -1332,19 +1332,19 @@
         <v>1.87</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P4">
-        <v>7.55</v>
+        <v>7.4</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.31</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P5">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="R5">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="S5">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="T5">
-        <v>4.94</v>
+        <v>5.6</v>
       </c>
       <c r="U5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V5">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="W5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1163,25 +1163,25 @@
         <v>8.6</v>
       </c>
       <c r="AA5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AB5">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AC5">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AD5">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AE5">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AF5">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AG5">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.96</v>
       </c>
       <c r="AK5">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O6">
-        <v>3.63</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
         <v>2.38</v>
@@ -1302,7 +1302,7 @@
         <v>2.09</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
         <v>3.1</v>
@@ -1314,10 +1314,10 @@
         <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.25</v>
@@ -1326,10 +1326,10 @@
         <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
         <v>2.78</v>
@@ -1338,13 +1338,13 @@
         <v>1.34</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
         <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
         <v>1.84</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1178,7 +1178,7 @@
         <v>1.68</v>
       </c>
       <c r="AF5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AG5">
         <v>3.65</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="P6">
         <v>3.8</v>
@@ -1308,10 +1308,10 @@
         <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
         <v>1.1</v>
@@ -1329,13 +1329,13 @@
         <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
         <v>2.78</v>
       </c>
       <c r="AD6">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
         <v>1.08</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1311,7 +1311,7 @@
         <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.1</v>
@@ -1329,7 +1329,7 @@
         <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
         <v>2.78</v>
@@ -1450,55 +1450,55 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="O7">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P7">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q7">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="S7">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="T7">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="U7">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y7">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="Z7">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="AA7">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AB7">
         <v>1.4</v>
       </c>
       <c r="AC7">
-        <v>4.98</v>
+        <v>5.94</v>
       </c>
       <c r="AD7">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE7">
         <v>1.01</v>
@@ -1523,7 +1523,7 @@
         <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="O7">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q7">
         <v>3.04</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>7.4</v>
+        <v>7.69</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1142,13 +1142,13 @@
         <v>1.08</v>
       </c>
       <c r="T5">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>1.75</v>
       </c>
       <c r="V5">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="W5">
         <v>1.33</v>
@@ -1157,10 +1157,10 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AA5">
         <v>1.18</v>
@@ -1172,7 +1172,7 @@
         <v>1.56</v>
       </c>
       <c r="AD5">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AE5">
         <v>1.68</v>
@@ -1317,7 +1317,7 @@
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.25</v>
@@ -1326,25 +1326,25 @@
         <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
         <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
         <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>3.47</v>
+        <v>2.9</v>
       </c>
       <c r="P3">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="P4">
-        <v>7.69</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q4">
         <v>1.62</v>
@@ -979,37 +979,37 @@
         <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="U4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V4">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z4">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB4">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AC4">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AD4">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE4">
         <v>1.2</v>
@@ -1034,7 +1034,7 @@
         <v>1.12</v>
       </c>
       <c r="AK4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
         <v>2.09</v>
@@ -1326,7 +1326,7 @@
         <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
         <v>1.93</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q9">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1133,7 +1133,7 @@
         <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="R5">
         <v>2.65</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="O7">
         <v>2.95</v>
       </c>
       <c r="P7">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="Q7">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S7">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="T7">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U7">
         <v>4.02</v>
@@ -1480,50 +1480,50 @@
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Z7">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AA7">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AB7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC7">
-        <v>5.94</v>
+        <v>6.03</v>
       </c>
       <c r="AD7">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE7">
         <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG7">
+        <v>1.53</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.36</v>
+      </c>
+      <c r="AK7">
         <v>1.6</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.33</v>
-      </c>
-      <c r="AK7">
-        <v>1.57</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1459,16 +1459,16 @@
         <v>3.08</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R7">
         <v>1.85</v>
       </c>
       <c r="S7">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="T7">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="U7">
         <v>4.02</v>
@@ -1483,10 +1483,10 @@
         <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Z7">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AA7">
         <v>2.9</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
+        <v>1.83</v>
+      </c>
+      <c r="Q8">
+        <v>4.75</v>
+      </c>
+      <c r="R8">
+        <v>2.15</v>
+      </c>
+      <c r="S8">
+        <v>1.4</v>
+      </c>
+      <c r="T8">
+        <v>2.66</v>
+      </c>
+      <c r="U8">
+        <v>2.91</v>
+      </c>
+      <c r="V8">
+        <v>1.34</v>
+      </c>
+      <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.32</v>
+      </c>
+      <c r="Z8">
+        <v>3.06</v>
+      </c>
+      <c r="AA8">
+        <v>2.04</v>
+      </c>
+      <c r="AB8">
+        <v>1.71</v>
+      </c>
+      <c r="AC8">
+        <v>3.54</v>
+      </c>
+      <c r="AD8">
+        <v>1.26</v>
+      </c>
+      <c r="AE8">
+        <v>1.04</v>
+      </c>
+      <c r="AF8">
         <v>1.87</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1459,10 +1459,10 @@
         <v>3.08</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S7">
         <v>1.69</v>
@@ -1495,7 +1495,7 @@
         <v>1.36</v>
       </c>
       <c r="AC7">
-        <v>6.03</v>
+        <v>6.12</v>
       </c>
       <c r="AD7">
         <v>1.08</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -635,28 +635,28 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="Q2">
         <v>2.47</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="U2">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -665,19 +665,19 @@
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AC2">
         <v>3.34</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
         <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="V3">
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="AA3">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>3.74</v>
+        <v>3.24</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK3">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>9.619999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="Q4">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="R4">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T4">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="U4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
         <v>1.62</v>
@@ -991,7 +991,7 @@
         <v>1.15</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
         <v>1.11</v>
@@ -1000,25 +1000,25 @@
         <v>5.5</v>
       </c>
       <c r="AA4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AC4">
         <v>2.19</v>
       </c>
       <c r="AD4">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK4">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,22 +1124,22 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P5">
         <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>3.17</v>
+        <v>3.52</v>
       </c>
       <c r="R5">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="S5">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1148,10 +1148,10 @@
         <v>1.75</v>
       </c>
       <c r="V5">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="W5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,19 +1160,19 @@
         <v>1.05</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AA5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AB5">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AC5">
         <v>1.56</v>
       </c>
       <c r="AD5">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AE5">
         <v>1.68</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.96</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
         <v>1.21</v>
@@ -1622,25 +1622,25 @@
         <v>1.83</v>
       </c>
       <c r="Q8">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="V8">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.04</v>
@@ -1649,28 +1649,28 @@
         <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB8">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC8">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG8">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,43 +1776,43 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AA9">
         <v>2</v>
@@ -1821,19 +1821,19 @@
         <v>1.8</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P5">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q5">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R5">
         <v>2.69</v>
@@ -1172,7 +1172,7 @@
         <v>1.56</v>
       </c>
       <c r="AD5">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AE5">
         <v>1.68</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S6">
         <v>1.38</v>
@@ -1317,7 +1317,7 @@
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.25</v>
@@ -1335,10 +1335,10 @@
         <v>3.1</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
         <v>1.67</v>
@@ -1459,10 +1459,10 @@
         <v>3.08</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S7">
         <v>1.69</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O2">
         <v>3.15</v>
       </c>
       <c r="P2">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="Q2">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
+        <v>1.04</v>
+      </c>
+      <c r="X2">
         <v>1.03</v>
-      </c>
-      <c r="X2">
-        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AA2">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="O3">
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q3">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="U3">
         <v>2.76</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z3">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC3">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AD3">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P4">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R4">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="S4">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="V4">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z4">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA4">
+        <v>1.57</v>
+      </c>
+      <c r="AB4">
+        <v>2.2</v>
+      </c>
+      <c r="AC4">
+        <v>2.43</v>
+      </c>
+      <c r="AD4">
         <v>1.44</v>
       </c>
-      <c r="AB4">
-        <v>2.48</v>
-      </c>
-      <c r="AC4">
-        <v>2.19</v>
-      </c>
-      <c r="AD4">
-        <v>1.6</v>
-      </c>
       <c r="AE4">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
+        <v>1.9</v>
+      </c>
+      <c r="AG4">
         <v>1.75</v>
       </c>
-      <c r="AG4">
-        <v>1.91</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK4">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1290,34 +1290,34 @@
         <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R6">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="S6">
         <v>1.38</v>
       </c>
       <c r="T6">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.25</v>
@@ -1326,25 +1326,25 @@
         <v>3.6</v>
       </c>
       <c r="AA6">
+        <v>1.95</v>
+      </c>
+      <c r="AB6">
         <v>1.85</v>
       </c>
-      <c r="AB6">
-        <v>1.93</v>
-      </c>
       <c r="AC6">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -624,14 +624,14 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,7 +696,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "23", "90+2"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O4">
         <v>4.8</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P5">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q5">
         <v>3.54</v>
@@ -1139,7 +1139,7 @@
         <v>2.69</v>
       </c>
       <c r="S5">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1148,7 +1148,7 @@
         <v>1.75</v>
       </c>
       <c r="V5">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="W5">
         <v>1.3</v>
@@ -1166,16 +1166,16 @@
         <v>1.2</v>
       </c>
       <c r="AB5">
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AC5">
         <v>1.56</v>
       </c>
       <c r="AD5">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AE5">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AF5">
         <v>1.25</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1613,55 +1613,55 @@
         </is>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q8">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="U8">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z8">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AA8">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AB8">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC8">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
         <v>1.04</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
         <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U9">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
         <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z9">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC9">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "28", "75", "90+4"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,39 +1104,39 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="O5">
         <v>4.45</v>
       </c>
       <c r="P5">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="R5">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="S5">
         <v>1.14</v>
@@ -1145,43 +1145,43 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="V5">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="W5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z5">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA5">
         <v>1.2</v>
       </c>
       <c r="AB5">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="AC5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AD5">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AE5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AF5">
         <v>1.25</v>
       </c>
       <c r="AG5">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1190,41 +1190,41 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "55"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1293,28 +1293,28 @@
         <v>3.3</v>
       </c>
       <c r="P6">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="R6">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -1323,28 +1323,28 @@
         <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.6</v>
+        <v>4.11</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-10-05.xlsx
+++ b/jogos_2026-10-05.xlsx
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "23", "77"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "68"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="O7">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P7">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="R7">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S7">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T7">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
         <v>1.03</v>
@@ -1483,31 +1483,31 @@
         <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Z7">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AA7">
         <v>2.9</v>
       </c>
       <c r="AB7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC7">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="AD7">
         <v>1.08</v>
       </c>
       <c r="AE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P8">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q8">
         <v>4.25</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O9">
+        <v>3.45</v>
+      </c>
+      <c r="P9">
+        <v>2.16</v>
+      </c>
+      <c r="Q9">
         <v>3.4</v>
-      </c>
-      <c r="P9">
-        <v>2.1</v>
-      </c>
-      <c r="Q9">
-        <v>3.6</v>
       </c>
       <c r="R9">
         <v>2.11</v>
@@ -1794,13 +1794,13 @@
         <v>1.31</v>
       </c>
       <c r="T9">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
         <v>1.08</v>
@@ -1809,7 +1809,7 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
         <v>3.48</v>
@@ -1830,7 +1830,7 @@
         <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG9">
         <v>2.1</v>
